--- a/artfynd/A 17275-2025 artfynd.xlsx
+++ b/artfynd/A 17275-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,113 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124982299</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>539987</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6448665</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17275-2025 artfynd.xlsx
+++ b/artfynd/A 17275-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>124982299</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 17275-2025 artfynd.xlsx
+++ b/artfynd/A 17275-2025 artfynd.xlsx
@@ -986,11 +986,6 @@
       <c r="B5" t="n">
         <v>57793</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>NT</t>

--- a/artfynd/A 17275-2025 artfynd.xlsx
+++ b/artfynd/A 17275-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112942603</v>
       </c>
       <c r="B2" t="n">
-        <v>93731</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,7 +713,7 @@
         <v>540046</v>
       </c>
       <c r="R2" t="n">
-        <v>6448727</v>
+        <v>6448728</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112942631</v>
+        <v>112942604</v>
       </c>
       <c r="B3" t="n">
-        <v>93720</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540019</v>
+        <v>540089</v>
       </c>
       <c r="R3" t="n">
-        <v>6448721</v>
+        <v>6448747</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112942604</v>
+        <v>112942605</v>
       </c>
       <c r="B4" t="n">
-        <v>93731</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540089</v>
+        <v>540105</v>
       </c>
       <c r="R4" t="n">
-        <v>6448747</v>
+        <v>6448755</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,53 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124982299</v>
+        <v>112942631</v>
       </c>
       <c r="B5" t="n">
-        <v>57793</v>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nyhagen, Nyhagen, Ög</t>
+          <t>Eggeby-Hamra, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539987</v>
+        <v>540019</v>
       </c>
       <c r="R5" t="n">
-        <v>6448665</v>
+        <v>6448721</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,15 +1051,414 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127288085</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>540251</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6448599</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127288068</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79707</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>540274</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6448603</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124982299</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nyhagen, Nyhagen, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>539987</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6448665</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127288038</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hamra Solbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>540274</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6448610</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Stor och till synes frisk ask.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17275-2025 artfynd.xlsx
+++ b/artfynd/A 17275-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112942603</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112942604</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112942605</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112942631</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288085</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288068</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124982299</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1459,8 +1499,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288038</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>